--- a/output/pdf_financials_xlsx/LTHM.xlsx
+++ b/output/pdf_financials_xlsx/LTHM.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7.412599</v>
+        <v>-7.412599</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5.394822</v>
+        <v>-5.33466</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.093852</v>
+        <v>-1.093852</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>7.412599</v>
+        <v>-7.412599</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5.364741</v>
+        <v>-5.364741</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.093852</v>
+        <v>-1.093852</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>7.412599</v>
+        <v>-7.412599</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5.364741</v>
+        <v>-5.364741</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.093852</v>
+        <v>-1.093852</v>
       </c>
     </row>
     <row r="24">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>268.23705</v>
+        <v>-268.23705</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7.412599</v>
+        <v>-7.412599</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.394822</v>
+        <v>-5.33466</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.093852</v>
+        <v>-1.093852</v>
       </c>
     </row>
     <row r="28">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7.412599</v>
+        <v>-7.412599</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5.394822</v>
+        <v>-5.33466</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.093852</v>
+        <v>-1.093852</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.5575902226245834</v>
+        <v>-0.5638784852267998</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.684759</v>
+        <v>4.481802</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>3.476639</v>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>7.412599</v>
+        <v>-7.412599</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>5.364741</v>
+        <v>-5.364741</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>1.093852</v>
+        <v>-1.093852</v>
       </c>
     </row>
     <row r="100">
@@ -3342,7 +3342,11 @@
           <t>Reserve for warrants 10</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>1.797043</v>
       </c>
@@ -4950,10 +4954,10 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>5.364741</v>
+        <v>-5.364741</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>1.093852</v>
+        <v>-1.093852</v>
       </c>
     </row>
     <row r="73">
@@ -5916,10 +5920,10 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>7.412599</v>
+        <v>-7.412599</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>5.786847</v>
+        <v>-5.786847</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LTHM.xlsx
+++ b/output/pdf_financials_xlsx/LTHM.xlsx
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010122</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002095</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.412599</v>
+        <v>-7.402477</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.33466</v>
+        <v>-5.332565</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.093852</v>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.412599</v>
+        <v>-7.402477</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.33466</v>
+        <v>-5.332565</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.093852</v>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.621192</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.216069</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.515365</v>
       </c>
     </row>
     <row r="35">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.621192</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.216069</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.515365</v>
       </c>
     </row>
     <row r="37">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">

--- a/output/pdf_financials_xlsx/LTHM.xlsx
+++ b/output/pdf_financials_xlsx/LTHM.xlsx
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.668864</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.779163</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.267397</v>
       </c>
     </row>
     <row r="108">
@@ -3569,7 +3569,11 @@
           <t>Share-based compensation expense 12</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -4036,7 +4040,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>0.668864</v>
       </c>
